--- a/Kegiatan_yang_telah_terlaksana.xlsx
+++ b/Kegiatan_yang_telah_terlaksana.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suwarno2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7BBC9B9-F75E-4AA2-A628-DCC128F055FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C95A49C-F814-47CD-A767-167354D0ACA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{16D431E1-6F9E-4B9A-9A13-EB1936D0B2F6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
   <si>
     <t>No​</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Workshop dengan Mitsui Kazuki dari Jepang di Sekolah Notre Dame​</t>
   </si>
   <si>
-    <t>Int’l self-dev partnership​</t>
-  </si>
-  <si>
     <t>Int’l comdev partnership​</t>
   </si>
   <si>
@@ -218,12 +215,6 @@
     <t>Outbound​</t>
   </si>
   <si>
-    <t>3 mahasiswa B27​</t>
-  </si>
-  <si>
-    <t>1 mahasiswa B28​</t>
-  </si>
-  <si>
     <t>14.​</t>
   </si>
   <si>
@@ -369,6 +360,12 @@
   </si>
   <si>
     <t>Hibah terkait DH​ -&gt; Revenue research</t>
+  </si>
+  <si>
+    <t>3 mahasiswa B27​, 1 mahasiswa B28​</t>
+  </si>
+  <si>
+    <t>Int’l self-dev partnership​, Int’l comdev partnership​</t>
   </si>
 </sst>
 </file>
@@ -740,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CE2AAA-7858-44B8-B18B-2ABBA09EA836}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33.140625" customWidth="1"/>
@@ -775,485 +772,469 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
       <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
         <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
         <v>58</v>
       </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
         <v>73</v>
       </c>
-      <c r="C20" t="s">
-        <v>71</v>
-      </c>
       <c r="D20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
         <v>106</v>
-      </c>
-      <c r="B31" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Kegiatan_yang_telah_terlaksana.xlsx
+++ b/Kegiatan_yang_telah_terlaksana.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suwarno2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C95A49C-F814-47CD-A767-167354D0ACA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5844A75-B858-4575-8618-6295F51C42C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{16D431E1-6F9E-4B9A-9A13-EB1936D0B2F6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
   <si>
     <t>No​</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Notes (status, pelaporan, evaluasi)​</t>
   </si>
   <si>
-    <t>1.​</t>
-  </si>
-  <si>
     <t>Workshop dengan Mitsui Kazuki dari Jepang di Sekolah Notre Dame​</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
     <t>Comdev DONE​</t>
   </si>
   <si>
-    <t>2.​</t>
-  </si>
-  <si>
     <t>Guest lecture Mitsui Kazuki di kelas B28 Independent Learning​</t>
   </si>
   <si>
@@ -86,9 +80,6 @@
     <t>Teaching DONE​</t>
   </si>
   <si>
-    <t>3.​</t>
-  </si>
-  <si>
     <t>Guest lecture Mitsui Kazuki di kelas B29 Instructional Design​</t>
   </si>
   <si>
@@ -98,9 +89,6 @@
     <t>Teaching DONE ​</t>
   </si>
   <si>
-    <t>4.​</t>
-  </si>
-  <si>
     <t>Webinar EduNext​</t>
   </si>
   <si>
@@ -110,9 +98,6 @@
     <t>28 Feb​</t>
   </si>
   <si>
-    <t>5.​</t>
-  </si>
-  <si>
     <t>Marketing IIETE, JCC​</t>
   </si>
   <si>
@@ -125,36 +110,24 @@
     <t>​</t>
   </si>
   <si>
-    <t>6.​</t>
-  </si>
-  <si>
     <t>Marketing PPTJ, Balai Kartini​</t>
   </si>
   <si>
     <t>5 Feb​</t>
   </si>
   <si>
-    <t>7.​</t>
-  </si>
-  <si>
     <t>Narsum untuk Hiroshima Univ Indonesia Association​</t>
   </si>
   <si>
     <t>National comdev partnership​</t>
   </si>
   <si>
-    <t>8.​</t>
-  </si>
-  <si>
     <t>Sertifikasi W74 sudah 76%​</t>
   </si>
   <si>
     <t>Student certification​</t>
   </si>
   <si>
-    <t>9.​</t>
-  </si>
-  <si>
     <t>Diskusi dan follow up mahasiswa NR dan evaluasi beasiswa​</t>
   </si>
   <si>
@@ -164,9 +137,6 @@
     <t>Reaktif Jiwan B26, Hefri B25​</t>
   </si>
   <si>
-    <t>10.​</t>
-  </si>
-  <si>
     <t>Submit 2 proposal BIMA PKM​</t>
   </si>
   <si>
@@ -176,12 +146,6 @@
     <t>5 Jan​</t>
   </si>
   <si>
-    <t>11.​</t>
-  </si>
-  <si>
-    <t>Submit buku karya mahasiswa ke publisher (MK Integrated Social)​</t>
-  </si>
-  <si>
     <t>25% mahasiswa punya karya​</t>
   </si>
   <si>
@@ -191,9 +155,6 @@
     <t>11 mahasiswa terlibat​</t>
   </si>
   <si>
-    <t>12.​</t>
-  </si>
-  <si>
     <t>Pendampingan tracer study W72​</t>
   </si>
   <si>
@@ -206,27 +167,18 @@
     <t>9 alumni​</t>
   </si>
   <si>
-    <t>13.​</t>
-  </si>
-  <si>
     <t>Submit 3-4 mahasiswa ke Kanada, beasiswa SEED​</t>
   </si>
   <si>
     <t>Outbound​</t>
   </si>
   <si>
-    <t>14.​</t>
-  </si>
-  <si>
     <t>Mengajukan 1-2 mahasiswa summer school Uzbekistan​</t>
   </si>
   <si>
     <t>B28 Tsara, Adelia​</t>
   </si>
   <si>
-    <t>15.​</t>
-  </si>
-  <si>
     <t>Industry visit ke Google Educators​</t>
   </si>
   <si>
@@ -236,24 +188,15 @@
     <t>29 Jan​</t>
   </si>
   <si>
-    <t>16.​</t>
-  </si>
-  <si>
     <t>GLS-IPS​</t>
   </si>
   <si>
     <t>Nat teaching partnership​</t>
   </si>
   <si>
-    <t>17.​</t>
-  </si>
-  <si>
     <t>GLS-IPA​</t>
   </si>
   <si>
-    <t>18.​</t>
-  </si>
-  <si>
     <t>Diskusi MoU riset CoLearn di Kijang​</t>
   </si>
   <si>
@@ -263,33 +206,21 @@
     <t>Research DONE (diskusi MoU)​</t>
   </si>
   <si>
-    <t>19.​</t>
-  </si>
-  <si>
     <t>Diskusi baca data riset CoLearn​</t>
   </si>
   <si>
-    <t>20.​</t>
-  </si>
-  <si>
     <t>Submit 10 hibah BIMA penelitian​</t>
   </si>
   <si>
     <t>Menunggu pengumuman​</t>
   </si>
   <si>
-    <t>21.​</t>
-  </si>
-  <si>
     <t>Probono ERM​</t>
   </si>
   <si>
     <t>Scopus FM, MHS, research program​</t>
   </si>
   <si>
-    <t>22.​</t>
-  </si>
-  <si>
     <t>Proses MoU Multimedia Nusantara School​</t>
   </si>
   <si>
@@ -299,9 +230,6 @@
     <t>Mau dikirim ke HIPP. Belum dilaporkan.​</t>
   </si>
   <si>
-    <t>23.​</t>
-  </si>
-  <si>
     <t>Review proposal BRIN​</t>
   </si>
   <si>
@@ -311,33 +239,21 @@
     <t>Butuh undangan/sertif. Belum dilaporkan.​</t>
   </si>
   <si>
-    <t>24.​</t>
-  </si>
-  <si>
     <t>Penyusunan modul PPG Kemen.​</t>
   </si>
   <si>
     <t>Butuh undangan. Belum dilaporkan​</t>
   </si>
   <si>
-    <t>25.​</t>
-  </si>
-  <si>
     <t>Reviewer jurnal IJLTER​</t>
   </si>
   <si>
     <t>withdraw​</t>
   </si>
   <si>
-    <t>26.​</t>
-  </si>
-  <si>
     <t>Reviewer jurnal UNJ​</t>
   </si>
   <si>
-    <t>27.​</t>
-  </si>
-  <si>
     <t>Membuka payung penelitian Crowdbees​</t>
   </si>
   <si>
@@ -347,9 +263,6 @@
     <t>3 FM sudah buka. Realisasi mandiri​</t>
   </si>
   <si>
-    <t>28.​</t>
-  </si>
-  <si>
     <t>SMART Competition​</t>
   </si>
   <si>
@@ -366,14 +279,37 @@
   </si>
   <si>
     <t>Int’l self-dev partnership​, Int’l comdev partnership​</t>
+  </si>
+  <si>
+    <t>Submit buku Etnografi karya mahasiswa ke publisher (MK Integrated Social)​</t>
+  </si>
+  <si>
+    <t>Submit buku Kalkulus dengan Python (karya dosen)</t>
+  </si>
+  <si>
+    <t>HKI</t>
+  </si>
+  <si>
+    <t>Maret</t>
+  </si>
+  <si>
+    <t>1 FM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -401,8 +337,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -737,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CE2AAA-7858-44B8-B18B-2ABBA09EA836}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33.140625" customWidth="1"/>
@@ -748,496 +690,514 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B30" t="s">
         <v>75</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
         <v>76</v>
       </c>
-      <c r="C20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="E30" t="s">
         <v>77</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>